--- a/assets/2D/setup.xlsx
+++ b/assets/2D/setup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" tabRatio="600" firstSheet="2" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,11 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -64,12 +69,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -112,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +145,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -738,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM364"/>
+  <dimension ref="A1:AP364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.46484375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -4115,6 +4138,21 @@
           <t>qv_07</t>
         </is>
       </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>qv_08</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>qv_09</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>qv_10</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4203,6 +4241,15 @@
       <c r="AM47" t="n">
         <v>0</v>
       </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4271,25 +4318,34 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH48" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ48" t="n">
         <v>-2</v>
       </c>
       <c r="AK48" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM48" t="n">
         <v>-10</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AN48" t="n">
         <v>-20</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AO48" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="49">
@@ -4359,25 +4415,34 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH49" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI49" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ49" t="n">
         <v>-2</v>
       </c>
       <c r="AK49" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM49" t="n">
         <v>-10</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AN49" t="n">
         <v>-20</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AO49" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="50">
@@ -4467,6 +4532,15 @@
       <c r="AM50" t="n">
         <v>0</v>
       </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4535,25 +4609,34 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH51" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI51" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ51" t="n">
         <v>-2</v>
       </c>
       <c r="AK51" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM51" t="n">
         <v>-10</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AN51" t="n">
         <v>-20</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AO51" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="52">
@@ -4623,25 +4706,34 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ52" t="n">
         <v>-2</v>
       </c>
       <c r="AK52" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM52" t="n">
         <v>-10</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AN52" t="n">
         <v>-20</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AO52" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="53">
@@ -4731,6 +4823,15 @@
       <c r="AM53" t="n">
         <v>0</v>
       </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4799,25 +4900,34 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH54" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ54" t="n">
         <v>-2</v>
       </c>
       <c r="AK54" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM54" t="n">
         <v>-10</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AN54" t="n">
         <v>-20</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AO54" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="55">
@@ -4887,25 +4997,34 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ55" t="n">
         <v>-2</v>
       </c>
       <c r="AK55" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM55" t="n">
         <v>-10</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AN55" t="n">
         <v>-20</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AO55" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="56">
@@ -4995,6 +5114,15 @@
       <c r="AM56" t="n">
         <v>0</v>
       </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5063,25 +5191,34 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ57" t="n">
         <v>-2</v>
       </c>
       <c r="AK57" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM57" t="n">
         <v>-10</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AN57" t="n">
         <v>-20</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AO57" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="58">
@@ -5151,25 +5288,34 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ58" t="n">
         <v>-2</v>
       </c>
       <c r="AK58" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM58" t="n">
         <v>-10</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AN58" t="n">
         <v>-20</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AO58" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="59">
@@ -5259,6 +5405,15 @@
       <c r="AM59" t="n">
         <v>0</v>
       </c>
+      <c r="AN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5327,25 +5482,34 @@
         <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH60" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ60" t="n">
         <v>-2</v>
       </c>
       <c r="AK60" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM60" t="n">
         <v>-10</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AN60" t="n">
         <v>-20</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AO60" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="61">
@@ -5415,25 +5579,34 @@
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="AH61" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AJ61" t="n">
         <v>-2</v>
       </c>
       <c r="AK61" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM61" t="n">
         <v>-10</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AN61" t="n">
         <v>-20</v>
       </c>
-      <c r="AM61" t="n">
+      <c r="AO61" t="n">
         <v>-40</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="62">
@@ -5547,6 +5720,11 @@
         <f>+W63</f>
         <v/>
       </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Manual refinement</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5603,6 +5781,31 @@
         <f>+W64</f>
         <v/>
       </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>nper</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>perlen</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>nstp</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>tsmult</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5659,6 +5862,23 @@
         <f>+W65</f>
         <v/>
       </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>steady state</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5715,6 +5935,23 @@
         <f>+W66</f>
         <v/>
       </c>
+      <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Initial condition and step change occurs here</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5771,6 +6008,23 @@
         <f>+W67</f>
         <v/>
       </c>
+      <c r="AD67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>600</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Monthly time steps for 50 years</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5827,6 +6081,23 @@
         <f>+W68</f>
         <v/>
       </c>
+      <c r="AD68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>180000</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Annual time steps for 500 years</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5883,6 +6154,23 @@
         <f>+W69</f>
         <v/>
       </c>
+      <c r="AD69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Century time steps for 50k years</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5939,6 +6227,23 @@
         <f>+W70</f>
         <v/>
       </c>
+      <c r="AD70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>360000000</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Millenia time steps for 1M years</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5995,6 +6300,23 @@
         <f>+W71</f>
         <v/>
       </c>
+      <c r="AD71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>360000000</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>100kyr time steps for 1M years</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6163,6 +6485,11 @@
         <f>+W74</f>
         <v/>
       </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Adaptive time step</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6219,6 +6546,36 @@
         <f>+W75</f>
         <v/>
       </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>nper</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>perlen</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>nstp</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>tsmult</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>t1 (days)</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>perlen (years)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6275,6 +6632,25 @@
         <f>+W76</f>
         <v/>
       </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>180000</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.02550572114299</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI76">
+        <f>AE76/360</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6331,6 +6707,25 @@
         <f>+W77</f>
         <v/>
       </c>
+      <c r="AD77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.03963822776441</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI77">
+        <f>AE77/360</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6387,6 +6782,25 @@
         <f>+W78</f>
         <v/>
       </c>
+      <c r="AD78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.05322565498253</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI78">
+        <f>AE78/360</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6443,6 +6857,25 @@
         <f>+W79</f>
         <v/>
       </c>
+      <c r="AD79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.06661749588864</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI79">
+        <f>AE79/360</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6497,6 +6930,25 @@
       </c>
       <c r="AA80" s="1">
         <f>+W80</f>
+        <v/>
+      </c>
+      <c r="AD80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>720000000</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1.0746477694404</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI80">
+        <f>AE80/360</f>
         <v/>
       </c>
     </row>
@@ -16943,7 +17395,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
         <v>300</v>
@@ -17204,79 +17656,14 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18000</v>
+        <v>720000000</v>
       </c>
       <c r="C4" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Monthly time steps for 50 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>180000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Annual time steps for 500 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Century time steps for 50k years</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>360000000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Millenia time steps for 1M years</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n"/>
+        <v>1.075</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -18397,21 +18784,20 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0.000555555555555556</v>
+        <v>5.55555555555556e-05</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.000555555555555556</v>
+        <v>5.55555555555556e-05</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.000555555555555556</v>
+        <v>5.55555555555556e-05</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.000555555555555556</v>
+        <v>5.55555555555556e-05</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.000555555555555556</v>
-      </c>
-      <c r="G2" s="1" t="n"/>
+        <v>5.55555555555556e-05</v>
+      </c>
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
@@ -18436,7 +18822,6 @@
       <c r="F3" s="1" t="n">
         <v>0.000555555555555556</v>
       </c>
-      <c r="G3" s="1" t="n"/>
       <c r="I3" s="1" t="n"/>
       <c r="J3" s="1" t="n"/>
       <c r="K3" s="1" t="n"/>
@@ -18444,7 +18829,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.000555555555555556</v>
@@ -18461,7 +18846,6 @@
       <c r="F4" s="1" t="n">
         <v>0.000555555555555556</v>
       </c>
-      <c r="G4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="1" t="n"/>
@@ -18469,7 +18853,6 @@
       <c r="D5" s="1" t="n"/>
       <c r="E5" s="1" t="n"/>
       <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="n"/>
@@ -21194,52 +21577,52 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>par_name</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>ub</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>trans</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>ncell</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>kh_01</t>
         </is>
@@ -21273,13 +21656,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>kh_02</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.01</v>
+      <c r="B3" s="1" t="n">
+        <v>1e-08</v>
       </c>
       <c r="C3" t="n">
         <v>9e-06</v>
@@ -21307,7 +21690,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>kh_03</t>
         </is>
@@ -21341,13 +21724,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>kh_04</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.01</v>
+      <c r="B5" s="1" t="n">
+        <v>1e-08</v>
       </c>
       <c r="C5" t="n">
         <v>9e-06</v>
@@ -21375,7 +21758,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>kh_05</t>
         </is>
@@ -21409,7 +21792,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>kv_01</t>
         </is>
@@ -21443,13 +21826,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>kv_02</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.01</v>
+      <c r="B8" s="1" t="n">
+        <v>1e-08</v>
       </c>
       <c r="C8" t="n">
         <v>9.000000000000002e-07</v>
@@ -21477,7 +21860,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>kv_03</t>
         </is>
@@ -21511,13 +21894,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>kv_04</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.01</v>
+      <c r="B10" s="1" t="n">
+        <v>1e-08</v>
       </c>
       <c r="C10" t="n">
         <v>9.000000000000002e-07</v>
@@ -21545,7 +21928,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>kv_05</t>
         </is>
@@ -21579,7 +21962,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>sy_01</t>
         </is>
@@ -21613,7 +21996,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>sy_02</t>
         </is>
@@ -21647,7 +22030,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>sy_03</t>
         </is>
@@ -21681,7 +22064,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>sy_04</t>
         </is>
@@ -21715,7 +22098,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>sy_05</t>
         </is>
@@ -21749,12 +22132,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>ss_01</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.0001</v>
       </c>
       <c r="C17" t="n">
@@ -21783,12 +22166,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>ss_02</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="1" t="n">
         <v>0.0001</v>
       </c>
       <c r="C18" t="n">
@@ -21817,12 +22200,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>ss_03</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="1" t="n">
         <v>0.0001</v>
       </c>
       <c r="C19" t="n">
@@ -21851,12 +22234,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ss_04</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="1" t="n">
         <v>0.0001</v>
       </c>
       <c r="C20" t="n">
@@ -21885,12 +22268,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>ss_05</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="1" t="n">
         <v>0.0001</v>
       </c>
       <c r="C21" t="n">
@@ -21919,7 +22302,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>rech_01</t>
         </is>
@@ -21953,7 +22336,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>rech_02</t>
         </is>
@@ -21987,7 +22370,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>rech_03</t>
         </is>
@@ -22021,7 +22404,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>rech_04</t>
         </is>
@@ -22055,7 +22438,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>rech_05</t>
         </is>
@@ -22089,7 +22472,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>drn_cond_01</t>
         </is>
@@ -22118,12 +22501,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Conductivity of drain/river bed</t>
+          <t>Unc</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>drn_cond_02</t>
         </is>
@@ -22152,12 +22535,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Conductivity of drain/river bed</t>
+          <t>Aqt_01</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>drn_cond_03</t>
         </is>
@@ -22186,12 +22569,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Conductivity of drain/river bed</t>
+          <t>Caq_01</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>drn_cond_04</t>
         </is>
@@ -22220,12 +22603,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Conductivity of drain/river bed</t>
+          <t>Aqt_02</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>drn_cond_05</t>
         </is>
@@ -22254,12 +22637,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Conductivity of drain/river bed</t>
+          <t>Caq_02</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>q_0</t>
         </is>
@@ -22303,7 +22686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E266"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -22339,7 +22722,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UncAq</t>
+          <t>Unc_0_250</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -22348,19 +22731,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aqt 1</t>
+          <t>Unc_0_300</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22369,19 +22752,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Caq 1</t>
+          <t>Unc_0_350</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -22390,19 +22773,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aqt 2 </t>
+          <t>Unc_0_400</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -22411,7 +22794,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -22423,7 +22806,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Caq 2</t>
+          <t>Unc_0_450</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -22432,34 +22815,5473 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Caq 1 outcrop</t>
+          <t>Unc_0_500</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAD </t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Unc_0_550</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Unc_0_600</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Unc_1_250</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unc_1_300</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unc_1_350</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unc_1_400</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unc_1_450</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unc_1_500</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unc_1_550</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unc_1_600</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unc_2_250</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unc_2_300</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unc_2_350</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unc_2_400</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unc_2_450</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unc_2_500</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unc_2_550</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unc_2_600</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unc_3_250</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unc_3_300</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unc_3_350</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unc_3_400</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unc_3_450</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unc_3_500</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unc_3_550</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unc_3_600</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unc_4_250</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unc_4_300</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unc_4_350</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unc_4_400</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unc_4_450</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unc_4_500</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unc_4_550</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unc_4_600</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aqt1_5_200</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aqt1_5_250</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aqt1_5_300</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aqt1_5_350</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aqt1_5_400</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aqt1_5_450</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aqt1_5_500</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aqt1_5_550</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aqt1_5_600</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aqt1_6_200</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aqt1_6_250</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aqt1_6_300</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aqt1_6_350</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aqt1_6_400</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aqt1_6_450</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aqt1_6_500</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aqt1_6_550</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aqt1_6_600</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aqt1_7_200</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aqt1_7_250</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aqt1_7_300</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Aqt1_7_350</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aqt1_7_400</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Aqt1_7_450</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aqt1_7_500</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Aqt1_7_550</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Aqt1_7_600</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Aqt1_8_200</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Aqt1_8_250</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Aqt1_8_300</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Aqt1_8_350</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>8</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aqt1_8_400</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Aqt1_8_450</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Aqt1_8_500</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Aqt1_8_550</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Aqt1_8_600</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Aqt1_9_200</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Aqt1_9_250</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aqt1_9_300</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Aqt1_9_350</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Aqt1_9_400</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aqt1_9_450</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Aqt1_9_500</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Aqt1_9_550</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Aqt1_9_600</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>9</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Aqt1_10_100</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Aqt1_10_150</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Aqt1_10_200</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Caq1_10_250</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Caq1_10_300</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Caq1_10_350</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>10</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Caq1_10_400</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Caq1_10_450</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Caq1_10_500</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>10</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Caq1_10_550</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Caq1_10_600</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Caq1_11_100</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Caq1_11_150</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>11</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Caq1_11_200</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Caq1_11_250</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>11</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Caq1_11_300</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>11</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Caq1_11_350</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Caq1_11_400</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Caq1_11_450</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>11</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Caq1_11_500</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>11</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Caq1_11_550</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>11</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Caq1_11_600</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>11</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Caq1_12_100</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
         <v>12</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Caq1_12_150</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
         <v>150</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Caq1_12_200</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Caq1_12_250</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Caq1_12_300</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Caq1_12_350</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Caq1_12_400</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Caq1_12_450</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Caq1_12_500</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Caq1_12_550</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Caq1_12_600</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Caq1_13_100</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>13</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Caq1_13_150</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>13</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Caq1_13_200</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>13</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Caq1_13_250</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>13</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Caq1_13_300</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>13</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Caq1_13_350</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>13</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Caq1_13_400</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>13</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Caq1_13_450</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>13</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Caq1_13_500</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>13</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Caq1_13_550</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>13</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Caq1_13_600</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>13</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Caq1_14_100</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>14</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Caq1_14_150</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>14</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Caq1_14_200</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>14</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Caq1_14_250</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>14</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Caq1_14_300</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>14</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Caq1_14_350</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>14</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Caq1_14_400</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>14</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Caq1_14_450</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>14</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Caq1_14_500</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>14</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Caq1_14_550</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>14</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Caq1_14_600</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>14</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Aqt2_15_75</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>15</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Aqt2_15_100</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>15</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Aqt2_15_150</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>15</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Aqt2_15_200</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>15</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Aqt2_15_250</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>15</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Aqt2_15_300</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>15</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Aqt2_15_350</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>15</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Aqt2_15_400</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>15</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Aqt2_15_450</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>15</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Aqt2_15_500</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>15</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Aqt2_15_550</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>15</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Aqt2_15_600</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>15</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Aqt2_16_75</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>16</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Aqt2_16_100</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>16</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Aqt2_16_150</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>16</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Aqt2_16_200</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>16</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Aqt2_16_250</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>16</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Aqt2_16_300</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>16</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Aqt2_16_350</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>16</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Aqt2_16_400</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>16</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Aqt2_16_450</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>16</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Aqt2_16_500</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>16</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Aqt2_16_550</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>16</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Aqt2_16_600</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>16</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Aqt2_17_75</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>17</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Aqt2_17_100</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>17</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Aqt2_17_150</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>17</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Aqt2_17_200</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>17</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Aqt2_17_250</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>17</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Aqt2_17_300</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>17</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Aqt2_17_350</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>17</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Aqt2_17_400</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>17</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Aqt2_17_450</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>17</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Aqt2_17_500</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>17</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Aqt2_17_550</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>17</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Aqt2_17_600</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>17</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Aqt2_18_75</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>18</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Aqt2_18_100</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>18</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Aqt2_18_150</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>18</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Aqt2_18_200</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>18</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Aqt2_18_250</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>18</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Aqt2_18_300</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>18</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Aqt2_18_350</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>18</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Aqt2_18_400</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>18</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Aqt2_18_450</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>18</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Aqt2_18_500</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>18</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Aqt2_18_550</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>18</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Aqt2_18_600</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>18</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Aqt2_19_75</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>19</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Aqt2_19_100</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>19</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Aqt2_19_150</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>19</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Aqt2_19_200</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>19</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Aqt2_19_250</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>19</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Aqt2_19_300</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>19</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Aqt2_19_350</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>19</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Aqt2_19_400</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>19</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Aqt2_19_450</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>19</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Aqt2_19_500</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>19</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Aqt2_19_550</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>19</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Aqt2_19_600</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>19</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Caq2_20_25</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>20</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Caq2_20_75</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>20</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Caq2_20_100</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>20</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Caq2_20_150</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>20</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Caq2_20_200</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>20</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Caq2_20_250</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>20</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Caq2_20_300</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>20</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Caq2_20_350</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>20</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Caq2_20_400</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>20</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Caq2_20_450</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>20</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Caq2_20_500</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>20</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Caq2_20_550</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>20</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Caq2_20_600</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>20</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Caq2_21_25</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>21</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Caq2_21_75</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>21</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Caq2_21_100</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>21</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Caq2_21_150</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>21</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Caq2_21_200</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>21</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Caq2_21_250</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>21</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Caq2_21_300</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>21</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Caq2_21_350</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>21</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Caq2_21_400</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>21</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Caq2_21_450</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>21</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Caq2_21_500</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>21</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Caq2_21_550</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>21</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Caq2_21_600</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>21</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Caq2_22_25</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>22</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Caq2_22_75</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>22</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Caq2_22_100</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>22</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Caq2_22_150</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>22</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Caq2_22_200</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>22</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Caq2_22_250</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>22</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Caq2_22_300</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>22</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Caq2_22_350</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>22</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Caq2_22_400</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>22</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Caq2_22_450</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>22</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Caq2_22_500</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>22</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Caq2_22_550</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>22</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Caq2_22_600</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>22</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Caq2_23_25</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>23</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Caq2_23_75</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>23</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Caq2_23_100</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>23</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Caq2_23_150</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>23</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Caq2_23_200</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>23</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Caq2_23_250</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>23</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Caq2_23_300</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>23</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Caq2_23_350</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>23</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Caq2_23_400</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>23</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Caq2_23_450</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>23</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Caq2_23_500</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>23</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Caq2_23_550</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>23</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Caq2_23_600</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>23</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Caq2_24_25</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>24</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Caq2_24_75</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>24</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Caq2_24_100</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>24</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Caq2_24_150</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>24</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Caq2_24_200</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>24</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Caq2_24_250</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>24</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Caq2_24_300</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>24</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Caq2_24_350</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>24</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Caq2_24_400</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>24</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Caq2_24_450</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>24</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Caq2_24_500</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>24</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Caq2_24_550</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>24</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Caq2_24_600</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>24</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -22474,35 +28296,35 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>well_id</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>lay</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>col</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>q</t>
         </is>
@@ -22549,7 +28371,7 @@
         <v>400</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -22559,7 +28381,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
@@ -22571,7 +28393,7 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -22615,7 +28437,7 @@
         <v>399</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
@@ -22625,7 +28447,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
@@ -22637,7 +28459,7 @@
         <v>399</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -22681,7 +28503,7 @@
         <v>401</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -22691,7 +28513,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
@@ -22703,7 +28525,7 @@
         <v>401</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -22747,7 +28569,7 @@
         <v>402</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -22757,7 +28579,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
@@ -22769,7 +28591,7 @@
         <v>402</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -22813,7 +28635,7 @@
         <v>398</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -22823,7 +28645,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
@@ -22835,7 +28657,7 @@
         <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -22849,7 +28671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -22888,31 +28710,6 @@
           <t>qv_05</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>qv_06</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>qv_07</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>qv_08</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>qv_09</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>qv_10</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22938,21 +28735,6 @@
       <c r="G2" t="n">
         <v>-3</v>
       </c>
-      <c r="H2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22978,21 +28760,6 @@
       <c r="G3" t="n">
         <v>-3</v>
       </c>
-      <c r="H3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23018,21 +28785,6 @@
       <c r="G4" t="n">
         <v>-3</v>
       </c>
-      <c r="H4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23058,21 +28810,6 @@
       <c r="G5" t="n">
         <v>-3</v>
       </c>
-      <c r="H5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23097,21 +28834,6 @@
       </c>
       <c r="G6" t="n">
         <v>-3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-60</v>
       </c>
     </row>
   </sheetData>
@@ -23163,41 +28885,6 @@
           <t>qv_03</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>qv_04</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>qv_05</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>qv_06</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>qv_07</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>qv_08</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>qv_09</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>qv_10</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23220,27 +28907,6 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23248,7 +28914,7 @@
           <t>WELL_01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>3600000</v>
       </c>
       <c r="C3" t="n">
@@ -23263,27 +28929,6 @@
       <c r="F3" t="n">
         <v>-1</v>
       </c>
-      <c r="G3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23292,7 +28937,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -23306,27 +28951,6 @@
       <c r="F4" t="n">
         <v>-1</v>
       </c>
-      <c r="G4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23349,27 +28973,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23377,7 +28980,7 @@
           <t>WELL_02</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>3600000</v>
       </c>
       <c r="C6" t="n">
@@ -23392,27 +28995,6 @@
       <c r="F6" t="n">
         <v>-1</v>
       </c>
-      <c r="G6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23421,7 +29003,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -23435,27 +29017,6 @@
       <c r="F7" t="n">
         <v>-1</v>
       </c>
-      <c r="G7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23478,27 +29039,6 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23506,7 +29046,7 @@
           <t>WELL_03</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>3600000</v>
       </c>
       <c r="C9" t="n">
@@ -23521,27 +29061,6 @@
       <c r="F9" t="n">
         <v>-1</v>
       </c>
-      <c r="G9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23550,7 +29069,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -23564,27 +29083,6 @@
       <c r="F10" t="n">
         <v>-1</v>
       </c>
-      <c r="G10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23607,27 +29105,6 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23635,7 +29112,7 @@
           <t>WELL_04</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>3600000</v>
       </c>
       <c r="C12" t="n">
@@ -23650,27 +29127,6 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23679,7 +29135,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -23693,27 +29149,6 @@
       <c r="F13" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23736,27 +29171,6 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23764,7 +29178,7 @@
           <t>WELL_05</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>3600000</v>
       </c>
       <c r="C15" t="n">
@@ -23779,27 +29193,6 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-60</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23808,7 +29201,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>400000000</v>
+        <v>800000000</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -23821,27 +29214,6 @@
       </c>
       <c r="F16" t="n">
         <v>-1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-60</v>
       </c>
     </row>
     <row r="18">
